--- a/HallwayTestingSkript/TestSkriptTuhl.xlsx
+++ b/HallwayTestingSkript/TestSkriptTuhl.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23029"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A06ABC2-736B-1F4E-B541-50AD5B679A87}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\PSE\Qualitätssicherung\HallwayTestingSkript\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65303ADE-E7FC-468D-8FC1-C6784D12B792}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-37860" yWindow="940" windowWidth="36920" windowHeight="20300" xr2:uid="{3C26C6AC-0FB7-9743-AF3E-A8A9535F8FC9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{3C26C6AC-0FB7-9743-AF3E-A8A9535F8FC9}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,29 +33,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="219">
   <si>
     <t>Testskript T.U.H.L</t>
   </si>
   <si>
-    <t>Drücken sie auf den Button oben rechts mit dem Fragezeichen.</t>
-  </si>
-  <si>
     <t>Die Hilfeseite erscheint nun in deutscher Sprache.</t>
   </si>
   <si>
-    <t>Drücken sie 'Nach Hause'.</t>
-  </si>
-  <si>
-    <t>Die Thumbnails zum zugehörigen Manuskript werden ausgeklappt.</t>
-  </si>
-  <si>
     <t>Der Editor wird auf der zum Vorschaubild gehörigen Seite geöffnet.</t>
   </si>
   <si>
-    <t>Die Tabellenansicht wird geladen und ist persistent so wie sie sie beim öffnen des Editors verlassen haben.</t>
-  </si>
-  <si>
     <t>Öffnen der Hilfe und ändern der Sprache</t>
   </si>
   <si>
@@ -243,9 +236,6 @@
     <t>Die Tabelle wird wieder angezeigt, in der selben Konfiguration wie sie verlassen wurde.</t>
   </si>
   <si>
-    <t>Dies Spalte bei der der Haken gestzt wurde erscheint nun wieder und die Spalte in welcher er entfernt wurde ist nicht mehr sichtbar.</t>
-  </si>
-  <si>
     <t>3.18</t>
   </si>
   <si>
@@ -333,33 +323,12 @@
     <t>Das Skript sollte mit einem kompletten Index durchgeführt werden.</t>
   </si>
   <si>
-    <t>Stellen sie sicher dass die User Datenbank leer ist oder das sie nur mit Pseudonymen arbeiten die es noch nicht gibt.</t>
-  </si>
-  <si>
     <t>Öffnen der Anwendung</t>
   </si>
   <si>
-    <t>Öffnen sie Tuhl in einem Browser.</t>
-  </si>
-  <si>
     <t>Betätigen Sie den 'submit' Button ohne ein Pseudonym eingegeben zu haben.</t>
   </si>
   <si>
-    <t>Geben sie ein Pseudonym ein, z.B. 'Max Mustermann' und bestätigen sie die Eingabe über den'submit' Button.</t>
-  </si>
-  <si>
-    <t>Wählen sie im Dropdownmenü mit dem Titel 'language' die deutsche Flagge oder die Option 'german' aus (hier variiert die Auswahlanzeige je nach Browser und Betriebssystem)</t>
-  </si>
-  <si>
-    <t>Ändern sie nun erneut die Sprache zu Englisch.</t>
-  </si>
-  <si>
-    <t>Wählen sie Seite 3 der Tabelle, mithilfe der Zahlen-buttons am unteren Rand der Tabelle aus.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verändern Sie die Spalten der Tabelle: - verstecken sie mind. eine der Spalten mithilfe des Menü im Spalten Kopf (3 kleine Punkte) - verändern Sie die Reihenfolge der Spalten idem Sie eine Spalte am Spaltenkopf nehmen und an die gewünschte Stelle ziehen - verändern Sie die Breite von mindestens einer der Spalten indem sie den Rand anklicken und verschieben. Versuchen Sie auch die erste Spalte (mit den Buttons) zu verschieben und die Größe zu ändern. </t>
-  </si>
-  <si>
     <t>Betätigen Sie den Button zum Anzeigen der nächsten Seite.</t>
   </si>
   <si>
@@ -378,9 +347,6 @@
     <t>Wählen Sie 20 als Anzahl der angezeigten Ergebnisse aus.</t>
   </si>
   <si>
-    <t>Klicken sie auf den Pfeil im Kopf einer beliebeigen Spalte.</t>
-  </si>
-  <si>
     <t>Klicken Sie auf den Button um auf die letzte Seite der Tabelle zu gelangen.</t>
   </si>
   <si>
@@ -396,12 +362,6 @@
     <t>Klicken Sie doppelt auf eine der Reihen.</t>
   </si>
   <si>
-    <t>Betätigen Sie die checkbox 'Always show Thumbnails'.</t>
-  </si>
-  <si>
-    <t>Entfernen Sie den Haken in der checkbox ' Always show Thumbnails'.</t>
-  </si>
-  <si>
     <t>Betätigen Sie den Button 'Reset columns'.</t>
   </si>
   <si>
@@ -411,15 +371,9 @@
     <t>Gehen Sie wieder aus dem Dropdownmenü heraus und verstecken Sie 2 Spalten über die 3 Punkte im Spaltenkopf. Öffnen Sie anschlißend wieder das Dropdownmenü.</t>
   </si>
   <si>
-    <t>Setzen Sie nun einen der entfernten Haken und entfernen sie einen der noch gesetzten. Bestätigen Sie die Auswahl über 'Apply'.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Betätigen Sie den 'Reset Columns' Button. </t>
   </si>
   <si>
-    <t>Betätigen Sie den zurück Button.</t>
-  </si>
-  <si>
     <t>Betätigen Sie den Button am Anfang einer der Reihen zum Öffnen des Editors.</t>
   </si>
   <si>
@@ -528,14 +482,119 @@
     <t>Geben Sie das Pseudonym von 1.3 ein und bestätigen Sie die Eingabe mit dem 'Submit' Button.</t>
   </si>
   <si>
-    <t>Tuhl wird geöffnet und ein Modal zur Eingabe des Pseudonym erscheint.</t>
-  </si>
-  <si>
     <t>Das Modal wird nicht geschlossen und es erscheint die Auffordeung ein Pseudonym einzugeben.</t>
   </si>
   <si>
+    <t>Eine Hilfeseite mit Allgemeinen Informationen zur Bedienung von Tuhl wird geöfnet. Die Sprache ist Englisch.</t>
+  </si>
+  <si>
+    <t>Sie gelangen zurück in die Tableview Ansicht. Diese sieht aus wie in 1.3, allerdings ist die Sprache nun auf Deutsch.</t>
+  </si>
+  <si>
+    <t>Die Tableview Ansicht erscheint nun auf Englisch.</t>
+  </si>
+  <si>
+    <t>Die Ergebnisse der Tabelle werden entsprechend geladen. Am unteren Rand der Tabelle ist nun der Button mit der Zahl 3 hervorgehoben.</t>
+  </si>
+  <si>
+    <t>Die Ergebnisse der nächsten Seite werden angezeigt, der Button mit der Zahl 4 ist hervorgehoben. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent.</t>
+  </si>
+  <si>
+    <t>Die Ergebnissse der ersten Seite werden angezeigt, der Button mit der Zahl 1 ist hervorgehoben. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent.</t>
+  </si>
+  <si>
+    <t>Die Ergebnissse der letzten Seite werden angezeigt, der Button mit der entsprechenden Zahl ist nun hervorgehoben. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent.</t>
+  </si>
+  <si>
+    <t>Die Ergebnissse der vorherigen Seite werden angezeigt, der Button mit der entsprechenden Zahl ist hervorgehoben. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent.</t>
+  </si>
+  <si>
+    <t>Die Tabelle Zeigt nun 20 Ergebnisse an. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent.</t>
+  </si>
+  <si>
+    <t>Die Ergebnisse werden aufsteigend nach der gewählten Spalte sortiert. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent. Die Tabelle ist auf Seite 1.</t>
+  </si>
+  <si>
+    <t>Die Vorschaubilder zum zugehörigen Manuskript werden unterhalb der angeklickten Reihe angezeigt. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent.</t>
+  </si>
+  <si>
+    <t>Auch hier werden die zugehörigen Vorschaubilder unterhalb der Reihe angezeigt. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent.</t>
+  </si>
+  <si>
+    <t>Es werden alle Vorschaubilder zu allen Reihen angezeigt. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent.</t>
+  </si>
+  <si>
+    <t>Auch hier werden die Vorschaubilder zu allen Reihen sofort angezeigt. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent.</t>
+  </si>
+  <si>
+    <t>Die Vorschaubilder zu dieser Reihe werden nun nicht mehr angezeigt. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent.</t>
+  </si>
+  <si>
+    <t>Es werden Checkboxen für jede Spalte außer der 'Id' und der 'Buttons' Spalte angezeigt. Alle sind gesetzt.</t>
+  </si>
+  <si>
+    <t>Im DropdownMenü sind nun die Haken der versteckten Spalten nicht mehr gesetzt.</t>
+  </si>
+  <si>
+    <t>Es sind nun alle Spalten wieder sichtbar.</t>
+  </si>
+  <si>
+    <t>Alle Häckchen sind gesetzt.</t>
+  </si>
+  <si>
+    <t>Der Editor wird auf der ersten Seite des zugehörigen Manuskripts geöffnet.</t>
+  </si>
+  <si>
+    <t>Die ausgewählten Filter erscheinen nun links und in der Spalte. Die Eingabefelder sind leer.</t>
+  </si>
+  <si>
+    <t>Die bereits ausgewählten Filter sind jetzt ausgegraut und können nicht mehr ausgewählt werden.</t>
+  </si>
+  <si>
+    <t>Alle noch nicht ausgewählten Filter werden ausgewählt.</t>
+  </si>
+  <si>
+    <t>Keine Filter sind mehr ausgewählt.</t>
+  </si>
+  <si>
+    <t>Der neue Filter erscheint nun auch links in der Spalte.</t>
+  </si>
+  <si>
+    <t>Die Suchergebnisse entsprechen den Filtern.</t>
+  </si>
+  <si>
+    <t>Die Suchergebniss werden neu geladen, entsprechend der 2 noch vorhandenen Filter. Die Tabelle befindet sich auf Seite 1.</t>
+  </si>
+  <si>
+    <t>Seite 3 mit den entsprechenden Suchergebnissen wird angezeigt.</t>
+  </si>
+  <si>
+    <t>Die Ergebnisse werden entsprechend der Filter und des Suchbegriffs angezeigt und sollten mit denen aud 5.15 überinstimmen.</t>
+  </si>
+  <si>
+    <t>Die Ergebnisse werden entsprechend des Suchbegriffs angezeigt. Und stimmen mit denen aus 5.18 überein.</t>
+  </si>
+  <si>
+    <t>Alle Funktionen funktonieren analog zu den vorherigen Durchläufen.</t>
+  </si>
+  <si>
+    <t>Die Seite wird wie bei 1.3 geladen.</t>
+  </si>
+  <si>
+    <t>Für alle Manuskripte werden die Vorschaubilder angezeigt.</t>
+  </si>
+  <si>
+    <t>Die Seite wird nun wierder genauso geladen wie in 7.4.</t>
+  </si>
+  <si>
+    <t>Die Seite wird so geladen wie nach 7.7.</t>
+  </si>
+  <si>
+    <t>Dieses Skript dient zum Testen der Funktionen der Anwendung T.U.H.L. Führen Sie alle Schritte nacheinander aus und überprüfen sie ob die Funtionalität dem beschriebenen erwarteten Verhalten entspricht. Tragen Sie eine 1 in das Ergebnisspalte ein falls Fehler auftreten und erläutern Sie das Problem im Kommentarfeld.</t>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve">Das Modal wird geschlossen und die Tableview Ansicht wird geöffnet.  Es werden keine Filter angezeigt und das Suchfeld ist leer. In der Tabelle sind alle Manuskripte welche im Index sind vorhanden, sie befindet sich auf der ersten Seite, die Anzahl der Ergebnisse pro Seite ist 10 und die Ergebnisse sind aufsteigend nach der 'Id'-Spalte sortiert. Dies wird im Folgenden als </t>
+      <t xml:space="preserve">Das Modal wird geschlossen und die Tableview Ansicht wird geöffnet.  Es werden keine Filter angezeigt und das Suchfeld ist leer. In der Tabelle sind alle Manuskripte, welche im Index sind, vorhanden. Sie befindet sich auf der ersten Seite. Die Anzahl der Ergebnisse pro Seite ist 10 und die Ergebnisse sind aufsteigend nach der 'Id'-Spalte sortiert. Dies wird im Folgenden als </t>
     </r>
     <r>
       <rPr>
@@ -560,149 +619,107 @@
     </r>
   </si>
   <si>
-    <t>Eine Hilfeseite mit Allgemeinen Informationen zur Bedienung von Tuhl wird geöfnet. Die Sprache ist Englisch.</t>
-  </si>
-  <si>
-    <t>Sie gelangen zurück in die Tableview Ansicht. Diese sieht aus wie in 1.3, allerdings ist die Sprache nun auf Deutsch.</t>
-  </si>
-  <si>
-    <t>Die Tableview Ansicht erscheint nun auf Englisch.</t>
-  </si>
-  <si>
-    <t>Die Ergebnisse der Tabelle werden entsprechend geladen. Am unteren Rand der Tabelle ist nun der Button mit der Zahl 3 hervorgehoben.</t>
-  </si>
-  <si>
-    <t>Die Erste Spalte lässt sich weder verschieben, noch lässt sich ihre Größe ändern, die 'id'-Spalte kann nicht versteckt verden. Alle andern Spalten lassen sich nach Ihren Wünschen manipulieren.</t>
-  </si>
-  <si>
-    <t>Die Ergebnisse der nächsten Seite werden angezeigt, der Button mit der Zahl 4 ist hervorgehoben. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent.</t>
-  </si>
-  <si>
-    <t>Die Ergebnissse der ersten Seite werden angezeigt, der Button mit der Zahl 1 ist hervorgehoben. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent.</t>
-  </si>
-  <si>
-    <t>Die Ergebnissse der letzten Seite werden angezeigt, der Button mit der entsprechenden Zahl ist nun hervorgehoben. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent.</t>
-  </si>
-  <si>
-    <t>Die Ergebnissse der vorherigen Seite werden angezeigt, der Button mit der entsprechenden Zahl ist hervorgehoben. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent.</t>
-  </si>
-  <si>
-    <t>Die Sortierung ist nun umgekehrt und die Tabelle wieder auf Seite 1. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent. Der Pfeil welcher die Sortierung anzeigt ist nun umgedreht.</t>
-  </si>
-  <si>
-    <t>Die Tabelle Zeigt nun 20 Ergebnisse an. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent.</t>
-  </si>
-  <si>
-    <t>Die Ergebnisse werden aufsteigend nach der gewählten Spalte sortiert. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent. Die Tabelle ist auf Seite 1.</t>
-  </si>
-  <si>
-    <t>Es wird minestens ein Ergebniss angezeigt. Die angezeigte Seitenzahl ist kleiner als in Schritt 3.5. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent.</t>
-  </si>
-  <si>
-    <t>Die Vorschaubilder zum zugehörigen Manuskript werden unterhalb der angeklickten Reihe angezeigt. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent.</t>
-  </si>
-  <si>
-    <t>Auch hier werden die zugehörigen Vorschaubilder unterhalb der Reihe angezeigt. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent.</t>
-  </si>
-  <si>
-    <t>Es werden alle Vorschaubilder zu allen Reihen angezeigt. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent.</t>
-  </si>
-  <si>
-    <t>Auch hier werden die Vorschaubilder zu allen Reihen sofort angezeigt. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent.</t>
-  </si>
-  <si>
-    <t>Die Vorschaubilder zu dieser Reihe werden nun nicht mehr angezeigt. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent.</t>
-  </si>
-  <si>
-    <t>Alle zuvor angezeigten Vorschaubilder Verschwinden. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent.</t>
-  </si>
-  <si>
-    <t>Es werden Checkboxen für jede Spalte außer der 'Id' und der 'Buttons' Spalte angezeigt. Alle sind gesetzt.</t>
-  </si>
-  <si>
-    <t>Im DropdownMenü sind nun die Haken der versteckten Spalten nicht mehr gesetzt.</t>
-  </si>
-  <si>
-    <t>Es sind nun alle Spalten wieder sichtbar.</t>
-  </si>
-  <si>
-    <t>Alle Häckchen sind gesetzt.</t>
-  </si>
-  <si>
-    <t>Der Editor wird auf der ersten Seite des zugehörigen Manuskripts geöffnet.</t>
-  </si>
-  <si>
-    <t>Die ausgewählten Filter erscheinen nun links und in der Spalte. Die Eingabefelder sind leer.</t>
-  </si>
-  <si>
-    <t>Die bereits ausgewählten Filter sind jetzt ausgegraut und können nicht mehr ausgewählt werden.</t>
-  </si>
-  <si>
-    <t>Alle noch nicht ausgewählten Filter werden ausgewählt.</t>
-  </si>
-  <si>
-    <t>Keine Filter sind mehr ausgewählt.</t>
-  </si>
-  <si>
-    <t>Der neue Filter erscheint nun auch links in der Spalte.</t>
-  </si>
-  <si>
-    <t>Die Suchergebnisse entsprechen den Filtern.</t>
-  </si>
-  <si>
-    <t>Die Suchergebniss werden neu geladen, entsprechend der 2 noch vorhandenen Filter. Die Tabelle befindet sich auf Seite 1.</t>
-  </si>
-  <si>
-    <t>Die Filter in der Spalte werden gelöscht und die Tabelle wieder mit allen Ergebnissen die im Index vorhanden sind angezeigt.</t>
-  </si>
-  <si>
-    <t>Seite 3 mit den entsprechenden Suchergebnissen wird angezeigt.</t>
-  </si>
-  <si>
-    <t>Die Ergebnisse in der Tabelle werden entsprechend des Suchbegriffs neu geladen. (Eventuell ist dies nicht ganz einsichtlich, da auch die Annotationen und TextKarten nach dem Suchbegriff durchsucht werden und diese nicht in der Tabelle angezeigt werden.) Die Tabelle befindet sich auf Seite 1.</t>
-  </si>
-  <si>
-    <t>Die Ergebnisse sollten nun mit denen aud 5.14 überieinstimmen</t>
-  </si>
-  <si>
-    <t>Die Ergebnisse werden entsprechend der Filter und des Suchbegriffs angezeigt und sollten mit denen aud 5.15 überinstimmen.</t>
-  </si>
-  <si>
-    <t>Die Ergebnisse werden entsprechend des Suchbegriffs angezeigt. Und stimmen mit denen aus 5.18 überein.</t>
-  </si>
-  <si>
-    <t>Alle Funktionen funktonieren analog zu den vorherigen Durchläufen.</t>
-  </si>
-  <si>
-    <t>Die Seite wird wie bei 1.3 geladen.</t>
-  </si>
-  <si>
-    <t>Die Tabelle wird nun mit allen Einstellungen wie sie in 7.1 getroffen wurden geladen. Auch die Filter und die Suche werden angezeigt und angewendet.</t>
-  </si>
-  <si>
-    <t>Für alle Manuskripte werden die Vorschaubilder angezeigt.</t>
-  </si>
-  <si>
-    <t>Die Seite wird nun wierder genauso geladen wie in 7.4.</t>
-  </si>
-  <si>
-    <t>Tuhl wird geöffnet, ein Modal zur Eingabe des Pseudonyms erscheint.</t>
-  </si>
-  <si>
-    <t>Die Seite wird so geladen wie nach 7.7.</t>
-  </si>
-  <si>
-    <t>Dieses Skript dient zum Testen der Funktionen der Anwendung T.U.H.L. Führen Sie alle Schritte nacheinander aus und überprüfen sie ob die Funtionalität dem beschriebenen erwarteten Verhalten entspricht. Tragen Sie eine 1 in das Ergebnisspalte ein falls Fehler auftreten und erläutern Sie das Problem im Kommentarfeld.</t>
-  </si>
-  <si>
-    <t>*sinnvoll bedeutet, dass es genügend Suchergebnisse gibt um beispielsweise 2 Seiten zu füllen, ausßerdem sollte einigermaßen identifizierbar sein ob die Filter/Suche richtig funtonieren.</t>
+    <t>Wählen sie im Dropdownmenü mit dem Titel 'language' die deutsche Flagge oder die Option 'GE' aus (hier variiert die Auswahlanzeige je nach Browser und Betriebssystem)</t>
+  </si>
+  <si>
+    <t>Die Erste Spalte lässt sich weder verschieben, noch lässt sich ihre Größe ändern, die 'id'-Spalte kann nicht versteckt verden. Alle andern Spalten lassen sich nach ihren Wünschen manipulieren.</t>
+  </si>
+  <si>
+    <t>Die Sortierung ist nun umgekehrt und die Tabelle wieder auf Seite 1. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent. Der Pfeil, welcher die Sortierung anzeigt, ist nun umgedreht.</t>
+  </si>
+  <si>
+    <t>Es wird minestens ein Ergebnis angezeigt. Die angezeigte Seitenzahl ist kleiner als in Schritt 3.5. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent.</t>
+  </si>
+  <si>
+    <t>Betätigen Sie die Checkbox 'Always show Thumbnails'.</t>
+  </si>
+  <si>
+    <t>Entfernen Sie den Haken in der Checkbox ' Always show Thumbnails'.</t>
+  </si>
+  <si>
+    <t>Alle zuvor angezeigten Vorschaubilder verschwinden. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent.</t>
+  </si>
+  <si>
+    <t>Setzen Sie nun einen der entfernten Haken und entfernen sie einen der noch Gesetzten. Bestätigen Sie die Auswahl über 'Apply'.</t>
+  </si>
+  <si>
+    <t>Die Spalte, bei welcher der Haken gesetzt wurde, erscheint nun wieder und die Spalte in welcher er entfernt wurde ist nicht mehr sichtbar.</t>
+  </si>
+  <si>
+    <t>Betätigen Sie den Zurück-Button.</t>
+  </si>
+  <si>
+    <t>Die Vorschaubilder zum zugehörigen Manuskript werden ausgeklappt.</t>
+  </si>
+  <si>
+    <t>Die Tabellenansicht wird geladen und ist persistent so wie Sie sie beim öffnen des Editors verlassen haben.</t>
+  </si>
+  <si>
+    <t>Die Vorschaubilder wird geladen und ist persistent so wie Sie sie beim öffnen des Editors verlassen haben.</t>
+  </si>
+  <si>
+    <t>Die Filter in der Spalte werden gelöscht und die Tabelle wieder mit allen Ergebnissen, die im Index vorhanden sind, angezeigt.</t>
+  </si>
+  <si>
+    <t>Die Ergebnisse in der Tabelle werden entsprechend des Suchbegriffs neu geladen. (Eventuell ist dies nicht ganz ersichtlich, da auch die Annotationen und Textkarten nach dem Suchbegriff durchsucht werden und diese nicht in der Tabelle angezeigt werden.) Die Tabelle befindet sich auf Seite 1.</t>
+  </si>
+  <si>
+    <t>Es werden wieder alle Manuskripte, die im Index vorhanden sind, angezeigt.</t>
+  </si>
+  <si>
+    <t>Die Ergebnisse sollten nun mit denen aus 5.14 überieinstimmen</t>
+  </si>
+  <si>
+    <t>*sinnvoll bedeutet, dass es genügend Suchergebnisse gibt um beispielsweise 2 Seiten zu füllen. Ausßerdem sollte einigermaßen identifizierbar sein, ob die Filter/Suche richtig funktonieren.</t>
+  </si>
+  <si>
+    <t>Klicken Sie auf den 'Edit' Button neben dem Pseudonym und geben Sie ein neues Pseudonym ein. Bestätigen Sie dieses mit 'Ok'.</t>
+  </si>
+  <si>
+    <t>Die Tabelle wird nun mit allen Einstellungen, wie sie in 7.1 getroffen wurden, geladen. Auch die Filter und die Suche werden angezeigt und angewendet.</t>
+  </si>
+  <si>
+    <t>Bearbeiten Sie erneut das Pseudonym und geben Sie das ein, was Sie bei 1.3 eingegeben hatten, bestätigen Sie mit 'Ok'.</t>
+  </si>
+  <si>
+    <t>TUHL wird geöffnet. Ein Modal zur Eingabe des Pseudonyms erscheint.</t>
+  </si>
+  <si>
+    <t>Stellen Sie sicher dass die User-Datenbank leer ist oder, dass sie nur mit Pseudonymen arbeiten die es noch nicht gibt.</t>
+  </si>
+  <si>
+    <t>Öffnen Sie TUHL in einem Browser.</t>
+  </si>
+  <si>
+    <t>TUHL wird geöffnet und ein Modal zur Eingabe des Pseudonym erscheint.</t>
+  </si>
+  <si>
+    <t>Geben sie ein Pseudonym ein, z.B. 'Max Mustermann' und bestätigen Sie die Eingabe über den 'submit' Button.</t>
+  </si>
+  <si>
+    <t>Drücken Sie auf den Button oben rechts mit dem Fragezeichen.</t>
+  </si>
+  <si>
+    <t>Drücken Sie 'Nach Hause'.</t>
+  </si>
+  <si>
+    <t>Ändern Sie nun erneut die Sprache zu Englisch.</t>
+  </si>
+  <si>
+    <t>Wählen Sie Seite 3 der Tabelle mithilfe der Zahlen-Buttons am unteren Rand der Tabelle aus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verändern Sie die Spalten der Tabelle: - verstecken Sie mind. eine der Spalten mithilfe des Menü im Spaltenkopf (3 kleine Punkte) - verändern Sie die Reihenfolge der Spalten indem Sie eine Spalte am Spaltenkopf nehmen und an die gewünschte Stelle ziehen - verändern Sie die Breite von mindestens einer der Spalten indem Sie den Rand anklicken und verschieben. Versuchen Sie auch die erste Spalte (mit den Buttons) zu verschieben und die Größe zu ändern. </t>
+  </si>
+  <si>
+    <t>Klicken Sie auf den Pfeil im Kopf einer beliebeigen Spalte.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -732,12 +749,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri (Textkörper)"/>
-    </font>
-    <font>
-      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri (Textkörper)"/>
@@ -808,7 +819,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -832,74 +843,71 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1376,142 +1384,142 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3766C35E-265C-7941-A176-9F3B5A5BA0EB}">
   <dimension ref="A1:F88"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="4.6640625" style="8" customWidth="1"/>
-    <col min="2" max="2" width="58.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="58.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="40.33203125" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" style="32"/>
+    <col min="1" max="1" width="4.625" style="8" customWidth="1"/>
+    <col min="2" max="2" width="58.625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="58.625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="40.375" customWidth="1"/>
+    <col min="6" max="6" width="10.875" style="30"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="9" customFormat="1" ht="20" thickBot="1">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" s="10" customFormat="1" ht="86" thickTop="1">
-      <c r="A2" s="11"/>
-      <c r="B2" s="13" t="s">
-        <v>213</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="D2" s="25">
+    <row r="1" spans="1:6" s="31" customFormat="1" ht="19.5" thickBot="1">
+      <c r="A1" s="31" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="9" customFormat="1" ht="90.75" thickTop="1">
+      <c r="A2" s="10"/>
+      <c r="B2" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2" s="23">
         <f>SUM(D11:D88)</f>
         <v>0</v>
       </c>
-      <c r="F2" s="27"/>
-    </row>
-    <row r="3" spans="1:6" s="10" customFormat="1" ht="19">
-      <c r="A3" s="11"/>
-      <c r="B3" s="13"/>
-      <c r="F3" s="27"/>
-    </row>
-    <row r="4" spans="1:6" s="21" customFormat="1" ht="17">
-      <c r="A4" s="19"/>
-      <c r="B4" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="D4" s="21" t="s">
+      <c r="F2" s="25"/>
+    </row>
+    <row r="3" spans="1:6" s="9" customFormat="1" ht="18.75">
+      <c r="A3" s="10"/>
+      <c r="B3" s="12"/>
+      <c r="F3" s="25"/>
+    </row>
+    <row r="4" spans="1:6" s="19" customFormat="1">
+      <c r="A4" s="17"/>
+      <c r="B4" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" s="26"/>
+    </row>
+    <row r="5" spans="1:6" s="14" customFormat="1" ht="18.75">
+      <c r="A5" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F5" s="27"/>
+    </row>
+    <row r="6" spans="1:6" s="9" customFormat="1" ht="18.75">
+      <c r="A6" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="F6" s="25"/>
+    </row>
+    <row r="7" spans="1:6" s="9" customFormat="1" ht="18.75">
+      <c r="A7" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="F7" s="25"/>
+    </row>
+    <row r="8" spans="1:6" s="16" customFormat="1" ht="31.5">
+      <c r="A8" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="F8" s="28"/>
+    </row>
+    <row r="9" spans="1:6" s="9" customFormat="1" ht="18.75">
+      <c r="A9" s="10"/>
+      <c r="F9" s="25"/>
+    </row>
+    <row r="10" spans="1:6" s="7" customFormat="1">
+      <c r="A10" s="11">
+        <v>1</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C10" s="6"/>
+      <c r="F10" s="29"/>
+    </row>
+    <row r="11" spans="1:6" ht="31.5">
+      <c r="A11" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="31.5">
+      <c r="A12" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E4" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="F4" s="28"/>
-    </row>
-    <row r="5" spans="1:6" s="16" customFormat="1" ht="19">
-      <c r="A5" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="F5" s="29"/>
-    </row>
-    <row r="6" spans="1:6" s="10" customFormat="1" ht="19">
-      <c r="A6" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="F6" s="27"/>
-    </row>
-    <row r="7" spans="1:6" s="10" customFormat="1" ht="19">
-      <c r="A7" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="F7" s="27"/>
-    </row>
-    <row r="8" spans="1:6" s="18" customFormat="1" ht="34">
-      <c r="A8" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="F8" s="30"/>
-    </row>
-    <row r="9" spans="1:6" s="10" customFormat="1" ht="19">
-      <c r="A9" s="11"/>
-      <c r="F9" s="27"/>
-    </row>
-    <row r="10" spans="1:6" s="7" customFormat="1" ht="17">
-      <c r="A10" s="12">
-        <v>1</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C10" s="6"/>
-      <c r="F10" s="31"/>
-    </row>
-    <row r="11" spans="1:6" ht="34">
-      <c r="A11" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="34">
-      <c r="A12" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="C12" s="3" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="170">
+    <row r="13" spans="1:6" ht="157.5">
       <c r="A13" s="8" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>105</v>
+        <v>212</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -1521,67 +1529,67 @@
       <c r="B14" s="1"/>
       <c r="C14" s="4"/>
     </row>
-    <row r="15" spans="1:6" s="7" customFormat="1" ht="17">
-      <c r="A15" s="12">
+    <row r="15" spans="1:6" s="7" customFormat="1">
+      <c r="A15" s="11">
         <v>2</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C15" s="6"/>
-      <c r="F15" s="31"/>
-    </row>
-    <row r="16" spans="1:6" ht="34">
+      <c r="F15" s="29"/>
+    </row>
+    <row r="16" spans="1:6" ht="31.5">
       <c r="A16" s="8" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="47.25">
+      <c r="A17" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="51">
-      <c r="A17" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>2</v>
-      </c>
       <c r="D17">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="34">
+    <row r="18" spans="1:6" ht="31.5">
       <c r="A18" s="8" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>3</v>
+        <v>214</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="17">
+    <row r="19" spans="1:6">
       <c r="A19" s="8" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>107</v>
+        <v>215</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1591,397 +1599,397 @@
       <c r="B20" s="1"/>
       <c r="C20" s="3"/>
     </row>
-    <row r="21" spans="1:6" s="7" customFormat="1" ht="17">
-      <c r="A21" s="12">
+    <row r="21" spans="1:6" s="7" customFormat="1">
+      <c r="A21" s="11">
         <v>3</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C21" s="6"/>
-      <c r="F21" s="31"/>
-    </row>
-    <row r="22" spans="1:6" ht="51">
+      <c r="F21" s="29"/>
+    </row>
+    <row r="22" spans="1:6" ht="47.25">
       <c r="A22" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="110.25">
+      <c r="A23" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="63">
+      <c r="A24" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="63">
+      <c r="A25" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="63">
+      <c r="A26" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B26" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="63">
+      <c r="A27" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="63">
+      <c r="A28" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="47.25">
+      <c r="A29" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="47.25">
+      <c r="A30" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="63">
+      <c r="A31" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="63">
+      <c r="A32" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="47.25">
+      <c r="A33" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="47.25">
+      <c r="A34" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="47.25">
+      <c r="A35" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="47.25">
+      <c r="A36" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="119">
-      <c r="A23" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" s="1" t="s">
+      <c r="C36" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="47.25">
+      <c r="A37" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="31.5">
+      <c r="A38" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="68">
-      <c r="A24" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" s="1" t="s">
+      <c r="C38" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="31.5">
+      <c r="A39" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="68">
-      <c r="A25" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="1" t="s">
+      <c r="C39" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="47.25">
+      <c r="A40" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="68">
-      <c r="A26" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="68">
-      <c r="A27" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" s="1" t="s">
+      <c r="C40" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="47.25">
+      <c r="A41" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="D27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="68">
-      <c r="A28" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="D28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="51">
-      <c r="A29" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="D29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="51">
-      <c r="A30" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="68">
-      <c r="A31" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="D31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="68">
-      <c r="A32" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="D32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="51">
-      <c r="A33" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="D33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="51">
-      <c r="A34" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="51">
-      <c r="A35" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="D35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="51">
-      <c r="A36" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="D36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="51">
-      <c r="A37" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="D37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="34">
-      <c r="A38" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="34">
-      <c r="A39" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="D39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="51">
-      <c r="A40" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="34">
-      <c r="A41" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C41" s="3" t="s">
+      <c r="C42" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="D41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="17">
-      <c r="A42" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="17">
-      <c r="A43" s="8" t="s">
-        <v>76</v>
-      </c>
       <c r="B43" s="1" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>191</v>
+        <v>168</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="1"/>
       <c r="C44" s="3"/>
     </row>
-    <row r="45" spans="1:6" s="7" customFormat="1" ht="17">
-      <c r="A45" s="12">
+    <row r="45" spans="1:6" s="7" customFormat="1">
+      <c r="A45" s="11">
         <v>4</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="C45" s="6"/>
-      <c r="F45" s="31"/>
-    </row>
-    <row r="46" spans="1:6" ht="34">
+      <c r="F45" s="29"/>
+    </row>
+    <row r="46" spans="1:6" ht="31.5">
       <c r="A46" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="31.5">
+      <c r="A47" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="31.5">
+      <c r="A49" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="31.5">
+      <c r="A50" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="34">
-      <c r="A47" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="17">
-      <c r="A48" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="34">
-      <c r="A49" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="34">
-      <c r="A50" s="8" t="s">
-        <v>43</v>
-      </c>
       <c r="B50" s="1" t="s">
-        <v>129</v>
+        <v>196</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>6</v>
+        <v>198</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -1991,145 +1999,145 @@
       <c r="B51" s="1"/>
       <c r="C51" s="3"/>
     </row>
-    <row r="52" spans="1:6" s="7" customFormat="1" ht="17">
-      <c r="A52" s="12">
+    <row r="52" spans="1:6" s="7" customFormat="1">
+      <c r="A52" s="11">
         <v>5</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="C52" s="6"/>
-      <c r="F52" s="31"/>
-    </row>
-    <row r="53" spans="1:6" ht="34">
+      <c r="F52" s="29"/>
+    </row>
+    <row r="53" spans="1:6" ht="31.5">
       <c r="A53" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="31.5">
+      <c r="A54" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="D53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="34">
-      <c r="A54" s="8" t="s">
+      <c r="B57" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="31.5">
+      <c r="A58" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="D54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="17">
-      <c r="A55" s="8" t="s">
+      <c r="B58" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="31.5">
+      <c r="A59" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="D55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="17">
-      <c r="A56" s="8" t="s">
+      <c r="B59" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="D56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="17">
-      <c r="A57" s="8" t="s">
+      <c r="B60" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="31.5">
+      <c r="A61" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="D57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="34">
-      <c r="A58" s="8" t="s">
+      <c r="B61" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="31.5">
+      <c r="A62" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B58" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="D58">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="34">
-      <c r="A59" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="17">
-      <c r="A60" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="34">
-      <c r="A61" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="D61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="34">
-      <c r="A62" s="8" t="s">
-        <v>53</v>
-      </c>
       <c r="B62" s="1" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>200</v>
@@ -2138,79 +2146,79 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="17">
+    <row r="63" spans="1:6">
       <c r="A63" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="78.75">
+      <c r="A64" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="31.5">
+      <c r="A65" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="31.5">
+      <c r="A67" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" ht="85">
-      <c r="A64" s="8" t="s">
+      <c r="B67" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="B64" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="D64">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="34">
-      <c r="A65" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="34">
-      <c r="A66" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D66">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="34">
-      <c r="A67" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D67">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="17">
-      <c r="A68" s="8" t="s">
-        <v>59</v>
-      </c>
       <c r="B68" s="1" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>203</v>
@@ -2219,247 +2227,247 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="34">
+    <row r="69" spans="1:6" ht="31.5">
       <c r="A69" s="8" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D69">
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="34">
+    <row r="70" spans="1:6" ht="31.5">
       <c r="A70" s="8" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D70">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="34">
+    <row r="71" spans="1:6" ht="31.5">
       <c r="A71" s="8" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="C71" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="D71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="31.5">
+      <c r="A72" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="38.25">
+      <c r="B73" s="24" t="s">
         <v>204</v>
       </c>
-      <c r="D71">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" ht="34">
-      <c r="A72" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C72" s="3" t="s">
+    </row>
+    <row r="74" spans="1:6" s="7" customFormat="1">
+      <c r="A74" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="B74" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="C74" s="22"/>
+      <c r="F74" s="29"/>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="31.5">
+      <c r="A76" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" s="7" customFormat="1">
+      <c r="A78" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="B78" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="C78" s="22"/>
+      <c r="F78" s="29"/>
+    </row>
+    <row r="79" spans="1:6" ht="94.5">
+      <c r="A79" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="31.5">
+      <c r="A80" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B80" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="D72">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" ht="45">
-      <c r="B73" s="26" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" s="7" customFormat="1" ht="17">
-      <c r="A74" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="B74" s="23" t="s">
-        <v>67</v>
-      </c>
-      <c r="C74" s="24"/>
-      <c r="F74" s="31"/>
-    </row>
-    <row r="75" spans="1:6" ht="17">
-      <c r="A75" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D75">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" ht="34">
-      <c r="A76" s="8" t="s">
+      <c r="C80" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="47.25">
+      <c r="A81" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="B76" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D76">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" s="7" customFormat="1" ht="17">
-      <c r="A78" s="22" t="s">
+      <c r="B81" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="31.5">
+      <c r="A83" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B78" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="C78" s="24"/>
-      <c r="F78" s="31"/>
-    </row>
-    <row r="79" spans="1:6" ht="102">
-      <c r="A79" s="8" t="s">
+      <c r="B83" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="31.5">
+      <c r="A84" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B79" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="D79">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" ht="34">
-      <c r="A80" s="8" t="s">
+      <c r="B84" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="B80" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="D80">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" ht="51">
-      <c r="A81" s="8" t="s">
+      <c r="B85" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="B81" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C81" s="2" t="s">
+      <c r="B86" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="31.5">
+      <c r="A87" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C87" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="D81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" ht="17">
-      <c r="A82" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="D82">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" ht="34">
-      <c r="A83" s="8" t="s">
+      <c r="D87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="31.5">
+      <c r="A88" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="B83" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="D83">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" ht="34">
-      <c r="A84" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="D84">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" ht="17">
-      <c r="A85" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D85">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" ht="17">
-      <c r="A86" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D86">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" ht="34">
-      <c r="A87" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D87">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" ht="34">
-      <c r="A88" s="8" t="s">
-        <v>90</v>
-      </c>
       <c r="B88" s="3" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>212</v>
+        <v>184</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -2535,6 +2543,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/HallwayTestingSkript/TestSkriptTuhl.xlsx
+++ b/HallwayTestingSkript/TestSkriptTuhl.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\PSE\Qualitätssicherung\HallwayTestingSkript\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicolettapuetz/Library/Mobile Documents/com~apple~CloudDocs/UNI/SS20/PSE/App/qualitaetssicherung/HallwayTestingSkript/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65303ADE-E7FC-468D-8FC1-C6784D12B792}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC9DC201-1B93-EF40-9E29-EDB8E6635459}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{3C26C6AC-0FB7-9743-AF3E-A8A9535F8FC9}"/>
+    <workbookView xWindow="-36860" yWindow="460" windowWidth="35700" windowHeight="20680" xr2:uid="{3C26C6AC-0FB7-9743-AF3E-A8A9535F8FC9}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="217">
   <si>
     <t>Testskript T.U.H.L</t>
   </si>
@@ -296,9 +296,6 @@
     <t>Die Vorschaubilder werden alle ausgeblendet.</t>
   </si>
   <si>
-    <t>Seite 2 mit den entsprechenden Suchergebnissen wird angezeigt</t>
-  </si>
-  <si>
     <t>5.19</t>
   </si>
   <si>
@@ -314,12 +311,6 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Errors:</t>
-  </si>
-  <si>
-    <t>Es muss ein TUHL Server laufen über den sie TUHL öffnen können.</t>
-  </si>
-  <si>
     <t>Das Skript sollte mit einem kompletten Index durchgeführt werden.</t>
   </si>
   <si>
@@ -332,12 +323,6 @@
     <t>Betätigen Sie den Button zum Anzeigen der nächsten Seite.</t>
   </si>
   <si>
-    <t>Betätigen Sie den Button um auf die Erste Seite zu gelangen.</t>
-  </si>
-  <si>
-    <t>Betätigen sie den Button um die vorherige Seite anzuzeigen.</t>
-  </si>
-  <si>
     <t>Klicken Sie auf den kleinen Pfeil im Kopf der 'Id'-Spalte.</t>
   </si>
   <si>
@@ -368,9 +353,6 @@
     <t>Öffnen Sie das 'Choose columns' Dropdownmenü.</t>
   </si>
   <si>
-    <t>Gehen Sie wieder aus dem Dropdownmenü heraus und verstecken Sie 2 Spalten über die 3 Punkte im Spaltenkopf. Öffnen Sie anschlißend wieder das Dropdownmenü.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Betätigen Sie den 'Reset Columns' Button. </t>
   </si>
   <si>
@@ -428,9 +410,6 @@
     <t>Geben Sie einen sinnvollen* Suchbegriff in die Suchleiste ein und drücken Sie auf 'Search'.</t>
   </si>
   <si>
-    <t xml:space="preserve">Leeren sie das Suchfeld und drücken sie erneut auf 'Search'. </t>
-  </si>
-  <si>
     <t xml:space="preserve">Erstellen Sie 2 sinnvolle* Filter und wenden Sie diese an. </t>
   </si>
   <si>
@@ -458,15 +437,6 @@
     <t>Entfernen Sie die Filter mit 'Clear filters'.</t>
   </si>
   <si>
-    <t>Wenden Sie einen sinnvollen* Filter an. Wenden sie eine sinnvolle* Suche an. Verändern Sie die Sortierung der Tabelle. Verändern Sie die Spalten der Tabelle, indem sie mind. eine verstecken, mind. eine verschieben und bei mind. einer die Breite verändern. Wählen Sie die Anzahl der angezeigten Ergebnisse als 20. Gehen Sie auf Seite 2 der Tabelle. Klappen Sie für eine Reihe die Vorschaubilder aus.</t>
-  </si>
-  <si>
-    <t>Klicken sie auf den 'Edit' Button neben dem Pseudonym und geben Sie ein neues Pseudonym ein. Bestätigen sie dieses mit 'Ok'.</t>
-  </si>
-  <si>
-    <t>Bearbeiten Sie erneut das Pseudonym und geben Sie das ein was Sie bei 1.3 eingegeben hatten, bestätigen Sie mit 'Ok'.</t>
-  </si>
-  <si>
     <t>Setzten Sie das Häkchen bei 'Always show thumbnails'.</t>
   </si>
   <si>
@@ -482,12 +452,6 @@
     <t>Geben Sie das Pseudonym von 1.3 ein und bestätigen Sie die Eingabe mit dem 'Submit' Button.</t>
   </si>
   <si>
-    <t>Das Modal wird nicht geschlossen und es erscheint die Auffordeung ein Pseudonym einzugeben.</t>
-  </si>
-  <si>
-    <t>Eine Hilfeseite mit Allgemeinen Informationen zur Bedienung von Tuhl wird geöfnet. Die Sprache ist Englisch.</t>
-  </si>
-  <si>
     <t>Sie gelangen zurück in die Tableview Ansicht. Diese sieht aus wie in 1.3, allerdings ist die Sprache nun auf Deutsch.</t>
   </si>
   <si>
@@ -500,18 +464,6 @@
     <t>Die Ergebnisse der nächsten Seite werden angezeigt, der Button mit der Zahl 4 ist hervorgehoben. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent.</t>
   </si>
   <si>
-    <t>Die Ergebnissse der ersten Seite werden angezeigt, der Button mit der Zahl 1 ist hervorgehoben. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent.</t>
-  </si>
-  <si>
-    <t>Die Ergebnissse der letzten Seite werden angezeigt, der Button mit der entsprechenden Zahl ist nun hervorgehoben. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent.</t>
-  </si>
-  <si>
-    <t>Die Ergebnissse der vorherigen Seite werden angezeigt, der Button mit der entsprechenden Zahl ist hervorgehoben. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent.</t>
-  </si>
-  <si>
-    <t>Die Tabelle Zeigt nun 20 Ergebnisse an. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent.</t>
-  </si>
-  <si>
     <t>Die Ergebnisse werden aufsteigend nach der gewählten Spalte sortiert. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent. Die Tabelle ist auf Seite 1.</t>
   </si>
   <si>
@@ -533,15 +485,9 @@
     <t>Es werden Checkboxen für jede Spalte außer der 'Id' und der 'Buttons' Spalte angezeigt. Alle sind gesetzt.</t>
   </si>
   <si>
-    <t>Im DropdownMenü sind nun die Haken der versteckten Spalten nicht mehr gesetzt.</t>
-  </si>
-  <si>
     <t>Es sind nun alle Spalten wieder sichtbar.</t>
   </si>
   <si>
-    <t>Alle Häckchen sind gesetzt.</t>
-  </si>
-  <si>
     <t>Der Editor wird auf der ersten Seite des zugehörigen Manuskripts geöffnet.</t>
   </si>
   <si>
@@ -569,9 +515,6 @@
     <t>Seite 3 mit den entsprechenden Suchergebnissen wird angezeigt.</t>
   </si>
   <si>
-    <t>Die Ergebnisse werden entsprechend der Filter und des Suchbegriffs angezeigt und sollten mit denen aud 5.15 überinstimmen.</t>
-  </si>
-  <si>
     <t>Die Ergebnisse werden entsprechend des Suchbegriffs angezeigt. Und stimmen mit denen aus 5.18 überein.</t>
   </si>
   <si>
@@ -584,13 +527,7 @@
     <t>Für alle Manuskripte werden die Vorschaubilder angezeigt.</t>
   </si>
   <si>
-    <t>Die Seite wird nun wierder genauso geladen wie in 7.4.</t>
-  </si>
-  <si>
     <t>Die Seite wird so geladen wie nach 7.7.</t>
-  </si>
-  <si>
-    <t>Dieses Skript dient zum Testen der Funktionen der Anwendung T.U.H.L. Führen Sie alle Schritte nacheinander aus und überprüfen sie ob die Funtionalität dem beschriebenen erwarteten Verhalten entspricht. Tragen Sie eine 1 in das Ergebnisspalte ein falls Fehler auftreten und erläutern Sie das Problem im Kommentarfeld.</t>
   </si>
   <si>
     <r>
@@ -619,18 +556,9 @@
     </r>
   </si>
   <si>
-    <t>Wählen sie im Dropdownmenü mit dem Titel 'language' die deutsche Flagge oder die Option 'GE' aus (hier variiert die Auswahlanzeige je nach Browser und Betriebssystem)</t>
-  </si>
-  <si>
-    <t>Die Erste Spalte lässt sich weder verschieben, noch lässt sich ihre Größe ändern, die 'id'-Spalte kann nicht versteckt verden. Alle andern Spalten lassen sich nach ihren Wünschen manipulieren.</t>
-  </si>
-  <si>
     <t>Die Sortierung ist nun umgekehrt und die Tabelle wieder auf Seite 1. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent. Der Pfeil, welcher die Sortierung anzeigt, ist nun umgedreht.</t>
   </si>
   <si>
-    <t>Es wird minestens ein Ergebnis angezeigt. Die angezeigte Seitenzahl ist kleiner als in Schritt 3.5. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent.</t>
-  </si>
-  <si>
     <t>Betätigen Sie die Checkbox 'Always show Thumbnails'.</t>
   </si>
   <si>
@@ -640,9 +568,6 @@
     <t>Alle zuvor angezeigten Vorschaubilder verschwinden. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent.</t>
   </si>
   <si>
-    <t>Setzen Sie nun einen der entfernten Haken und entfernen sie einen der noch Gesetzten. Bestätigen Sie die Auswahl über 'Apply'.</t>
-  </si>
-  <si>
     <t>Die Spalte, bei welcher der Haken gesetzt wurde, erscheint nun wieder und die Spalte in welcher er entfernt wurde ist nicht mehr sichtbar.</t>
   </si>
   <si>
@@ -652,12 +577,6 @@
     <t>Die Vorschaubilder zum zugehörigen Manuskript werden ausgeklappt.</t>
   </si>
   <si>
-    <t>Die Tabellenansicht wird geladen und ist persistent so wie Sie sie beim öffnen des Editors verlassen haben.</t>
-  </si>
-  <si>
-    <t>Die Vorschaubilder wird geladen und ist persistent so wie Sie sie beim öffnen des Editors verlassen haben.</t>
-  </si>
-  <si>
     <t>Die Filter in der Spalte werden gelöscht und die Tabelle wieder mit allen Ergebnissen, die im Index vorhanden sind, angezeigt.</t>
   </si>
   <si>
@@ -667,9 +586,6 @@
     <t>Es werden wieder alle Manuskripte, die im Index vorhanden sind, angezeigt.</t>
   </si>
   <si>
-    <t>Die Ergebnisse sollten nun mit denen aus 5.14 überieinstimmen</t>
-  </si>
-  <si>
     <t>*sinnvoll bedeutet, dass es genügend Suchergebnisse gibt um beispielsweise 2 Seiten zu füllen. Ausßerdem sollte einigermaßen identifizierbar sein, ob die Filter/Suche richtig funktonieren.</t>
   </si>
   <si>
@@ -679,24 +595,15 @@
     <t>Die Tabelle wird nun mit allen Einstellungen, wie sie in 7.1 getroffen wurden, geladen. Auch die Filter und die Suche werden angezeigt und angewendet.</t>
   </si>
   <si>
-    <t>Bearbeiten Sie erneut das Pseudonym und geben Sie das ein, was Sie bei 1.3 eingegeben hatten, bestätigen Sie mit 'Ok'.</t>
-  </si>
-  <si>
     <t>TUHL wird geöffnet. Ein Modal zur Eingabe des Pseudonyms erscheint.</t>
   </si>
   <si>
-    <t>Stellen Sie sicher dass die User-Datenbank leer ist oder, dass sie nur mit Pseudonymen arbeiten die es noch nicht gibt.</t>
-  </si>
-  <si>
     <t>Öffnen Sie TUHL in einem Browser.</t>
   </si>
   <si>
     <t>TUHL wird geöffnet und ein Modal zur Eingabe des Pseudonym erscheint.</t>
   </si>
   <si>
-    <t>Geben sie ein Pseudonym ein, z.B. 'Max Mustermann' und bestätigen Sie die Eingabe über den 'submit' Button.</t>
-  </si>
-  <si>
     <t>Drücken Sie auf den Button oben rechts mit dem Fragezeichen.</t>
   </si>
   <si>
@@ -713,6 +620,93 @@
   </si>
   <si>
     <t>Klicken Sie auf den Pfeil im Kopf einer beliebeigen Spalte.</t>
+  </si>
+  <si>
+    <t>Dieses Skript dient zum Testen der Funktionen der Anwendung T.U.H.L. Führen Sie alle Schritte nacheinander aus und überprüfen Sie ob die Funtionalität dem beschriebenen erwarteten Verhalten entspricht. Tragen Sie eine 1 in das Ergebnisspalte ein falls Fehler auftreten und erläutern Sie das Problem im Kommentarfeld.</t>
+  </si>
+  <si>
+    <t>Es muss ein TUHL Server laufen über den Sie TUHL öffnen können.</t>
+  </si>
+  <si>
+    <t>Stellen Sie sicher, dass die User-Datenbank leer ist oder dass Sie nur mit Pseudonymen arbeiten die es noch nicht gibt.</t>
+  </si>
+  <si>
+    <t>Geben Sie ein Pseudonym ein, z.B. 'Max Mustermann' und bestätigen Sie die Eingabe über den 'Submit' Button.</t>
+  </si>
+  <si>
+    <t>Das Modal wird nicht geschlossen und es erscheint die Aufforderung ein Pseudonym einzugeben.</t>
+  </si>
+  <si>
+    <t>Wählen Sie im Dropdownmenü mit dem Titel 'language' die deutsche Flagge oder die Option 'GE' aus (hier variiert die Auswahlanzeige je nach Browser und Betriebssystem)</t>
+  </si>
+  <si>
+    <t>Eine Hilfeseite mit allgemeinen Informationen zur Bedienung von Tuhl wird geöfnet. Die Sprache ist Englisch.</t>
+  </si>
+  <si>
+    <t>Betätigen Sie den Button um die vorherige Seite anzuzeigen.</t>
+  </si>
+  <si>
+    <t>Die erste Spalte lässt sich weder verschieben, noch lässt sich ihre Größe ändern, die 'Id'-Spalte kann nicht versteckt verden. Alle andern Spalten lassen sich nach Ihren Wünschen manipulieren.</t>
+  </si>
+  <si>
+    <t>Betätigen Sie den Button um auf die erste Seite zu gelangen.</t>
+  </si>
+  <si>
+    <t>Die Ergebnisse der letzten Seite werden angezeigt, der Button mit der entsprechenden Zahl ist nun hervorgehoben. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent.</t>
+  </si>
+  <si>
+    <t>Die Ergebnisse der ersten Seite werden angezeigt, der Button mit der Zahl 1 ist hervorgehoben. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent.</t>
+  </si>
+  <si>
+    <t>Die Ergebnisse der vorherigen Seite werden angezeigt, der Button mit der entsprechenden Zahl ist hervorgehoben. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent.</t>
+  </si>
+  <si>
+    <t>Die Tabelle zeigt nun 20 Ergebnisse an. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent.</t>
+  </si>
+  <si>
+    <t>Es wird mindestens ein Ergebnis angezeigt. Die angezeigte Seitenzahl ist kleiner als in Schritt 3.5. Die zuvor getroffenen Spalteneinstellungen (Reihenfolge, Breite, Sichtbakeit) sind persistent.</t>
+  </si>
+  <si>
+    <t>Setzen Sie nun einen der entfernten Haken und entfernen Sie einen der noch Gesetzten. Bestätigen Sie die Auswahl über 'Apply'.</t>
+  </si>
+  <si>
+    <t>Im Dropdownmenü sind nun die Haken der versteckten Spalten nicht mehr gesetzt.</t>
+  </si>
+  <si>
+    <t>Gehen Sie wieder aus dem Dropdownmenü heraus und verstecken Sie 2 Spalten über die 3 Punkte im Spaltenkopf. Öffnen Sie anschließend wieder das Dropdownmenü.</t>
+  </si>
+  <si>
+    <t>Alle Haken sind gesetzt.</t>
+  </si>
+  <si>
+    <t>Die Vorschaubilder wird geladen und ist persistent so wie Sie sie beim Öffnen des Editors verlassen haben.</t>
+  </si>
+  <si>
+    <t>Die Tabellenansicht wird geladen und ist persistent so wie Sie sie beim Öffnen des Editors verlassen haben.</t>
+  </si>
+  <si>
+    <t>Seite 2 mit den entsprechenden Suchergebnissen wird angezeigt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leeren Sie das Suchfeld und drücken Sie erneut auf 'Search'. </t>
+  </si>
+  <si>
+    <t>Die Ergebnisse sollten nun mit denen aus 5.14 übereinstimmen.</t>
+  </si>
+  <si>
+    <t>Die Ergebnisse werden entsprechend der Filter und des Suchbegriffs angezeigt und sollten mit denen aud 5.15 übereinstimmen.</t>
+  </si>
+  <si>
+    <t>Wenden Sie einen sinnvollen* Filter an. Wenden Sie eine sinnvolle* Suche an. Verändern Sie die Sortierung der Tabelle. Verändern Sie die Spalten der Tabelle, indem Sie mind. eine verstecken, mind. eine verschieben und bei mind. einer die Breite verändern. Wählen Sie die Anzahl der angezeigten Ergebnisse als 20. Gehen Sie auf Seite 2 der Tabelle. Klappen Sie für eine Reihe die Vorschaubilder aus.</t>
+  </si>
+  <si>
+    <t>Bearbeiten Sie erneut das Pseudonym und geben Sie das ein, was Sie bei 1.3 eingegeben hatten. Bestätigen Sie mit 'Ok'.</t>
+  </si>
+  <si>
+    <t>Die Seite wird nun wieder genauso geladen wie in 7.4.</t>
+  </si>
+  <si>
+    <t>Fehler:</t>
   </si>
 </sst>
 </file>
@@ -1383,28 +1377,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3766C35E-265C-7941-A176-9F3B5A5BA0EB}">
-  <dimension ref="A1:F88"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F89"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="4.625" style="8" customWidth="1"/>
-    <col min="2" max="2" width="58.625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="58.625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="40.375" customWidth="1"/>
-    <col min="6" max="6" width="10.875" style="30"/>
+    <col min="1" max="1" width="4.6640625" style="8" customWidth="1"/>
+    <col min="2" max="2" width="58.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="58.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="40.33203125" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" style="30"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="31" customFormat="1" ht="19.5" thickBot="1">
+    <row r="1" spans="1:6" s="31" customFormat="1" ht="20" thickBot="1">
       <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="9" customFormat="1" ht="90.75" thickTop="1">
+    <row r="2" spans="1:6" s="9" customFormat="1" ht="86" thickTop="1">
       <c r="A2" s="10"/>
       <c r="B2" s="12" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>93</v>
+        <v>216</v>
       </c>
       <c r="D2" s="23">
         <f>SUM(D11:D88)</f>
@@ -1412,12 +1406,12 @@
       </c>
       <c r="F2" s="25"/>
     </row>
-    <row r="3" spans="1:6" s="9" customFormat="1" ht="18.75">
+    <row r="3" spans="1:6" s="9" customFormat="1" ht="19">
       <c r="A3" s="10"/>
       <c r="B3" s="12"/>
       <c r="F3" s="25"/>
     </row>
-    <row r="4" spans="1:6" s="19" customFormat="1">
+    <row r="4" spans="1:6" s="19" customFormat="1" ht="17">
       <c r="A4" s="17"/>
       <c r="B4" s="18" t="s">
         <v>60</v>
@@ -1426,14 +1420,14 @@
         <v>61</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E4" s="19" t="s">
         <v>59</v>
       </c>
       <c r="F4" s="26"/>
     </row>
-    <row r="5" spans="1:6" s="14" customFormat="1" ht="18.75">
+    <row r="5" spans="1:6" s="14" customFormat="1" ht="19">
       <c r="A5" s="13" t="s">
         <v>58</v>
       </c>
@@ -1442,84 +1436,84 @@
       </c>
       <c r="F5" s="27"/>
     </row>
-    <row r="6" spans="1:6" s="9" customFormat="1" ht="18.75">
+    <row r="6" spans="1:6" s="9" customFormat="1" ht="19">
       <c r="A6" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="F6" s="25"/>
+    </row>
+    <row r="7" spans="1:6" s="9" customFormat="1" ht="19">
+      <c r="A7" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="B6" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="F6" s="25"/>
-    </row>
-    <row r="7" spans="1:6" s="9" customFormat="1" ht="18.75">
-      <c r="A7" s="15" t="s">
+      <c r="B7" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="F7" s="25"/>
+    </row>
+    <row r="8" spans="1:6" s="16" customFormat="1" ht="34">
+      <c r="A8" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="B7" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="F7" s="25"/>
-    </row>
-    <row r="8" spans="1:6" s="16" customFormat="1" ht="31.5">
-      <c r="A8" s="15" t="s">
-        <v>91</v>
-      </c>
       <c r="B8" s="16" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="F8" s="28"/>
     </row>
-    <row r="9" spans="1:6" s="9" customFormat="1" ht="18.75">
+    <row r="9" spans="1:6" s="9" customFormat="1" ht="19">
       <c r="A9" s="10"/>
       <c r="F9" s="25"/>
     </row>
-    <row r="10" spans="1:6" s="7" customFormat="1">
+    <row r="10" spans="1:6" s="7" customFormat="1" ht="17">
       <c r="A10" s="11">
         <v>1</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C10" s="6"/>
       <c r="F10" s="29"/>
     </row>
-    <row r="11" spans="1:6" ht="31.5">
+    <row r="11" spans="1:6" ht="34">
       <c r="A11" s="8" t="s">
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>211</v>
+        <v>181</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="31.5">
+    <row r="12" spans="1:6" ht="34">
       <c r="A12" s="8" t="s">
         <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>149</v>
+        <v>192</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="157.5">
+    <row r="13" spans="1:6" ht="170">
       <c r="A13" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>212</v>
+        <v>191</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -1529,7 +1523,7 @@
       <c r="B14" s="1"/>
       <c r="C14" s="4"/>
     </row>
-    <row r="15" spans="1:6" s="7" customFormat="1">
+    <row r="15" spans="1:6" s="7" customFormat="1" ht="17">
       <c r="A15" s="11">
         <v>2</v>
       </c>
@@ -1539,26 +1533,26 @@
       <c r="C15" s="6"/>
       <c r="F15" s="29"/>
     </row>
-    <row r="16" spans="1:6" ht="31.5">
+    <row r="16" spans="1:6" ht="34">
       <c r="A16" s="8" t="s">
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>213</v>
+        <v>182</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="47.25">
+    <row r="17" spans="1:6" ht="51">
       <c r="A17" s="8" t="s">
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>1</v>
@@ -1567,29 +1561,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="31.5">
+    <row r="18" spans="1:6" ht="34">
       <c r="A18" s="8" t="s">
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>214</v>
+        <v>183</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" ht="17">
       <c r="A19" s="8" t="s">
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>215</v>
+        <v>184</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1599,7 +1593,7 @@
       <c r="B20" s="1"/>
       <c r="C20" s="3"/>
     </row>
-    <row r="21" spans="1:6" s="7" customFormat="1">
+    <row r="21" spans="1:6" s="7" customFormat="1" ht="17">
       <c r="A21" s="11">
         <v>3</v>
       </c>
@@ -1609,236 +1603,236 @@
       <c r="C21" s="6"/>
       <c r="F21" s="29"/>
     </row>
-    <row r="22" spans="1:6" ht="47.25">
+    <row r="22" spans="1:6" ht="51">
       <c r="A22" s="8" t="s">
         <v>18</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="110.25">
+    <row r="23" spans="1:6" ht="136">
       <c r="A23" s="8" t="s">
         <v>19</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>217</v>
+        <v>186</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="63">
+    <row r="24" spans="1:6" ht="68">
       <c r="A24" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="63">
+    <row r="25" spans="1:6" ht="68">
       <c r="A25" s="8" t="s">
         <v>21</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>99</v>
+        <v>197</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>155</v>
+        <v>199</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="63">
+    <row r="26" spans="1:6" ht="68">
       <c r="A26" s="8" t="s">
         <v>22</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>156</v>
+        <v>198</v>
       </c>
       <c r="D26">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="63">
+    <row r="27" spans="1:6" ht="68">
       <c r="A27" s="8" t="s">
         <v>23</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>100</v>
+        <v>195</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>157</v>
+        <v>200</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="63">
+    <row r="28" spans="1:6" ht="68">
       <c r="A28" s="8" t="s">
         <v>24</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="D28">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="47.25">
+    <row r="29" spans="1:6" ht="51">
       <c r="A29" s="8" t="s">
         <v>25</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>218</v>
+        <v>187</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="47.25">
+    <row r="30" spans="1:6" ht="51">
       <c r="A30" s="8" t="s">
         <v>26</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>158</v>
+        <v>201</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="63">
+    <row r="31" spans="1:6" ht="68">
       <c r="A31" s="8" t="s">
         <v>27</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="D31">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="63">
+    <row r="32" spans="1:6" ht="68">
       <c r="A32" s="8" t="s">
         <v>28</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="47.25">
+    <row r="33" spans="1:6" ht="51">
       <c r="A33" s="8" t="s">
         <v>29</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="47.25">
+    <row r="34" spans="1:6" ht="51">
       <c r="A34" s="8" t="s">
         <v>30</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="47.25">
+    <row r="35" spans="1:6" ht="51">
       <c r="A35" s="8" t="s">
         <v>31</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="D35">
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="47.25">
+    <row r="36" spans="1:6" ht="51">
       <c r="A36" s="8" t="s">
         <v>32</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="47.25">
+    <row r="37" spans="1:6" ht="51">
       <c r="A37" s="8" t="s">
         <v>33</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="D37">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="31.5">
+    <row r="38" spans="1:6" ht="34">
       <c r="A38" s="8" t="s">
         <v>34</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>5</v>
@@ -1847,132 +1841,132 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="31.5">
+    <row r="39" spans="1:6" ht="34">
       <c r="A39" s="8" t="s">
         <v>67</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="D39">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="47.25">
+    <row r="40" spans="1:6" ht="51">
       <c r="A40" s="8" t="s">
         <v>68</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>111</v>
+        <v>205</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>166</v>
+        <v>204</v>
       </c>
       <c r="D40">
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="47.25">
+    <row r="41" spans="1:6" ht="51">
       <c r="A41" s="8" t="s">
         <v>69</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" ht="17">
       <c r="A42" s="8" t="s">
         <v>70</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="17">
       <c r="A43" s="8" t="s">
         <v>71</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>168</v>
+        <v>206</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="1"/>
       <c r="C44" s="3"/>
     </row>
-    <row r="45" spans="1:6" s="7" customFormat="1">
+    <row r="45" spans="1:6" s="7" customFormat="1" ht="17">
       <c r="A45" s="11">
         <v>4</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C45" s="6"/>
       <c r="F45" s="29"/>
     </row>
-    <row r="46" spans="1:6" ht="31.5">
+    <row r="46" spans="1:6" ht="34">
       <c r="A46" s="8" t="s">
         <v>35</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="D46">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="31.5">
+    <row r="47" spans="1:6" ht="34">
       <c r="A47" s="8" t="s">
         <v>36</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>196</v>
+        <v>171</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" ht="34">
       <c r="A48" s="8" t="s">
         <v>37</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>197</v>
+        <v>172</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="31.5">
+    <row r="49" spans="1:6" ht="34">
       <c r="A49" s="8" t="s">
         <v>38</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>2</v>
@@ -1981,15 +1975,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="31.5">
+    <row r="50" spans="1:6" ht="34">
       <c r="A50" s="8" t="s">
         <v>39</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>196</v>
+        <v>171</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -1999,106 +1993,106 @@
       <c r="B51" s="1"/>
       <c r="C51" s="3"/>
     </row>
-    <row r="52" spans="1:6" s="7" customFormat="1">
+    <row r="52" spans="1:6" s="7" customFormat="1" ht="17">
       <c r="A52" s="11">
         <v>5</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C52" s="6"/>
       <c r="F52" s="29"/>
     </row>
-    <row r="53" spans="1:6" ht="31.5">
+    <row r="53" spans="1:6" ht="34">
       <c r="A53" s="8" t="s">
         <v>40</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="31.5">
+    <row r="54" spans="1:6" ht="34">
       <c r="A54" s="8" t="s">
         <v>41</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="D54">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" spans="1:6" ht="17">
       <c r="A55" s="8" t="s">
         <v>42</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
+    <row r="56" spans="1:6" ht="17">
       <c r="A56" s="8" t="s">
         <v>43</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="D56">
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
+    <row r="57" spans="1:6" ht="17">
       <c r="A57" s="8" t="s">
         <v>44</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="D57">
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="31.5">
+    <row r="58" spans="1:6" ht="34">
       <c r="A58" s="8" t="s">
         <v>45</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="D58">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="31.5">
+    <row r="59" spans="1:6" ht="34">
       <c r="A59" s="8" t="s">
         <v>46</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>6</v>
@@ -2107,90 +2101,90 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" spans="1:6" ht="17">
       <c r="A60" s="8" t="s">
         <v>47</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="31.5">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="34">
       <c r="A61" s="8" t="s">
         <v>48</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="31.5">
+    <row r="62" spans="1:6" ht="34">
       <c r="A62" s="8" t="s">
         <v>49</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:6">
+    <row r="63" spans="1:6" ht="17">
       <c r="A63" s="8" t="s">
         <v>50</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" ht="78.75">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="85">
       <c r="A64" s="8" t="s">
         <v>51</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="31.5">
+    <row r="65" spans="1:6" ht="34">
       <c r="A65" s="8" t="s">
         <v>52</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>131</v>
+        <v>210</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>202</v>
+        <v>175</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" ht="34">
       <c r="A66" s="8" t="s">
         <v>53</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>8</v>
@@ -2199,12 +2193,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="31.5">
+    <row r="67" spans="1:6" ht="34">
       <c r="A67" s="8" t="s">
         <v>54</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>9</v>
@@ -2213,26 +2207,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" ht="17">
       <c r="A68" s="8" t="s">
         <v>55</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="31.5">
+    <row r="69" spans="1:6" ht="34">
       <c r="A69" s="8" t="s">
         <v>56</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>7</v>
@@ -2241,12 +2235,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="31.5">
+    <row r="70" spans="1:6" ht="34">
       <c r="A70" s="8" t="s">
         <v>57</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>10</v>
@@ -2255,40 +2249,40 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="31.5">
+    <row r="71" spans="1:6" ht="34">
       <c r="A71" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>178</v>
+        <v>212</v>
       </c>
       <c r="D71">
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="31.5">
+    <row r="72" spans="1:6" ht="34">
       <c r="A72" s="8" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="D72">
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="38.25">
+    <row r="73" spans="1:6" ht="45">
       <c r="B73" s="24" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" s="7" customFormat="1">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" s="7" customFormat="1" ht="17">
       <c r="A74" s="20" t="s">
         <v>64</v>
       </c>
@@ -2298,12 +2292,12 @@
       <c r="C74" s="22"/>
       <c r="F74" s="29"/>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" ht="17">
       <c r="A75" s="8" t="s">
         <v>72</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>65</v>
@@ -2312,12 +2306,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="31.5">
+    <row r="76" spans="1:6" ht="34">
       <c r="A76" s="8" t="s">
         <v>73</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>66</v>
@@ -2326,7 +2320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:6" s="7" customFormat="1">
+    <row r="78" spans="1:6" s="7" customFormat="1" ht="17">
       <c r="A78" s="20" t="s">
         <v>75</v>
       </c>
@@ -2336,142 +2330,146 @@
       <c r="C78" s="22"/>
       <c r="F78" s="29"/>
     </row>
-    <row r="79" spans="1:6" ht="94.5">
+    <row r="79" spans="1:6" ht="102">
       <c r="A79" s="8" t="s">
         <v>76</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>180</v>
+        <v>213</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>161</v>
       </c>
       <c r="D79">
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="31.5">
+    <row r="80" spans="1:6" ht="34">
       <c r="A80" s="8" t="s">
         <v>77</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>181</v>
+        <v>177</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>162</v>
       </c>
       <c r="D80">
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="47.25">
+    <row r="81" spans="1:4" ht="51">
       <c r="A81" s="8" t="s">
         <v>78</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>206</v>
+        <v>214</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>178</v>
       </c>
       <c r="D81">
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:4">
+    <row r="82" spans="1:4" ht="17">
       <c r="A82" s="8" t="s">
         <v>79</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>182</v>
+        <v>134</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>163</v>
       </c>
       <c r="D82">
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="31.5">
+    <row r="83" spans="1:4" ht="34">
       <c r="A83" s="8" t="s">
         <v>80</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>181</v>
+        <v>177</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>162</v>
       </c>
       <c r="D83">
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="31.5">
+    <row r="84" spans="1:4" ht="34">
       <c r="A84" s="8" t="s">
         <v>81</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>183</v>
+        <v>214</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>215</v>
       </c>
       <c r="D84">
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:4">
+    <row r="85" spans="1:4" ht="17">
       <c r="A85" s="8" t="s">
         <v>82</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="C85" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C85" s="3" t="s">
         <v>86</v>
       </c>
       <c r="D85">
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:4">
+    <row r="86" spans="1:4" ht="17">
       <c r="A86" s="8" t="s">
         <v>83</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>145</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="C86" s="3"/>
       <c r="D86">
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="31.5">
+    <row r="87" spans="1:4" ht="34">
       <c r="A87" s="8" t="s">
         <v>84</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>208</v>
+        <v>137</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="D87">
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="31.5">
+    <row r="88" spans="1:4" ht="34">
       <c r="A88" s="8" t="s">
         <v>85</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>184</v>
+        <v>138</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>164</v>
       </c>
       <c r="D88">
         <v>0</v>
       </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="C89" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
